--- a/static/samples/students_upload_sample.xlsx
+++ b/static/samples/students_upload_sample.xlsx
@@ -26,16 +26,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00888888"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,7 +57,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,71 +425,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>admin_no</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>first_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>last_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>gender</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>grade</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>stream</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>date_of_birth</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pathway</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>subjects</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>parent_phone</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>parent_email</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>parent_first_name</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>parent_last_name</t>
         </is>
@@ -531,12 +553,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MATH,ENG</t>
+          <t>MAT,ENG,PHY</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>0712345678</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>mary.kamau@gmail.com</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -586,14 +613,24 @@
           <t>2007-11-20</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sciences</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MATH,ENG,PHY</t>
+          <t>MAT,ENG,BIO</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>0723456789</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>janet.otieno@gmail.com</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -643,9 +680,14 @@
           <t>2008-01-05</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Arts</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MATH,ENG</t>
+          <t>ENG,HIST,GEO</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -653,6 +695,11 @@
           <t>0734567890</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>grace.wanjiku@gmail.com</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>Grace</t>
@@ -664,28 +711,68 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t># NOTE:</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n"/>
-      <c r="C6" s="1" t="n"/>
-      <c r="D6" s="1" t="n"/>
-      <c r="E6" s="1" t="n"/>
-      <c r="F6" s="1" t="n"/>
-      <c r="G6" s="1" t="n"/>
-      <c r="H6" s="1" t="n"/>
-      <c r="I6" s="1" t="inlineStr">
-        <is>
-          <t>Comma-separated subject CODES that match catalog-activated subjects (e.g. MTH,ENG,PHY). Unknown codes are skipped.</t>
-        </is>
-      </c>
-      <c r="J6" s="1" t="n"/>
-      <c r="K6" s="1" t="n"/>
-      <c r="L6" s="1" t="n"/>
-      <c r="M6" s="1" t="n"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2024004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dennis</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Maina</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Form 2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2007-06-22</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MAT,ENG,CHEM</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0745678901</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>peter.maina@gmail.com</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Maina</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
